--- a/product_upload/packages/51/file.xlsx
+++ b/product_upload/packages/51/file.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT101"/>
+  <dimension ref="A1:AU101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacture Name</t>
+          <t>Manufacturer Name</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -649,6 +649,11 @@
         </is>
       </c>
       <c r="AT1" t="inlineStr">
+        <is>
+          <t>Name / En</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -673,7 +678,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -844,6 +849,11 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
+          <t>Rivax</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
           <t>SKU-691506F6CDFB</t>
         </is>
       </c>
@@ -867,7 +877,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1034,6 +1044,11 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
+          <t>Rivax</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
           <t>SKU-506F2C51DB28</t>
         </is>
       </c>
@@ -1057,7 +1072,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1224,6 +1239,11 @@
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="inlineStr">
         <is>
+          <t>Rivax</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
           <t>SKU-3D8C53AEC239</t>
         </is>
       </c>
@@ -1247,7 +1267,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1414,6 +1434,11 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
+          <t>Nevotic</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
           <t>SKU-E947E4FD7ED3</t>
         </is>
       </c>
@@ -1437,7 +1462,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1592,6 +1617,11 @@
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="inlineStr">
         <is>
+          <t>Zolomid</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
           <t>SKU-849A5896AE35</t>
         </is>
       </c>
@@ -1615,7 +1645,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1774,6 +1804,11 @@
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="inlineStr">
         <is>
+          <t>Zolomid</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
           <t>SKU-7F937D944FF2</t>
         </is>
       </c>
@@ -1797,7 +1832,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1966,6 +2001,11 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
+          <t>SIMLANDI 40MG/0.4ML SOLUTION FOR INJECTION PFS</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
           <t>SKU-A9E1A40CD93F</t>
         </is>
       </c>
@@ -1989,7 +2029,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2154,6 +2194,11 @@
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="inlineStr">
         <is>
+          <t>SIMLANDI 40MG/0.4ML SOLUTION FOR INJECTION PFS</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
           <t>SKU-40BF5A3BA197</t>
         </is>
       </c>
@@ -2177,7 +2222,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2342,6 +2387,11 @@
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="inlineStr">
         <is>
+          <t xml:space="preserve">SIMLANDI 80MG/0.4ML SOLUTION FOR INJECTION PFS	</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
           <t>SKU-F4FCAEFED241</t>
         </is>
       </c>
@@ -2365,7 +2415,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2540,6 +2590,11 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
+          <t>Roneza</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
           <t>SKU-CEC1C736BA36</t>
         </is>
       </c>
@@ -2563,7 +2618,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2732,6 +2787,11 @@
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="inlineStr">
         <is>
+          <t>Roneza</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
           <t>SKU-FCD84D5A4E40</t>
         </is>
       </c>
@@ -2755,7 +2815,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2928,6 +2988,11 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
+          <t>Roneza</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
           <t>SKU-AD28791290F5</t>
         </is>
       </c>
@@ -2951,7 +3016,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3120,6 +3185,11 @@
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="inlineStr">
         <is>
+          <t>Roneza</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
           <t>SKU-B739A8B08197</t>
         </is>
       </c>
@@ -3143,7 +3213,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3318,6 +3388,11 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
+          <t>EpiPen 300 mcg per 0.3 ml</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
           <t>SKU-637CF4B36768</t>
         </is>
       </c>
@@ -3341,7 +3416,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3510,6 +3585,11 @@
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="inlineStr">
         <is>
+          <t>Koselugo</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
           <t>SKU-93E744318295</t>
         </is>
       </c>
@@ -3533,7 +3613,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3708,6 +3788,11 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
+          <t>Koselugo</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
           <t>SKU-6633C0259D63</t>
         </is>
       </c>
@@ -3731,7 +3816,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3894,6 +3979,11 @@
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="inlineStr">
         <is>
+          <t>EpiPen 150 mcg per  0.3 ml</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
           <t>SKU-C0EEC0847F38</t>
         </is>
       </c>
@@ -3917,7 +4007,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -4080,6 +4170,11 @@
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="inlineStr">
         <is>
+          <t>RYALTRIS</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
           <t>SKU-12BBAAE17981</t>
         </is>
       </c>
@@ -4103,7 +4198,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4270,6 +4365,11 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
+          <t>RYALTRIS</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
           <t>SKU-64D3FDFD508E</t>
         </is>
       </c>
@@ -4293,7 +4393,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4462,6 +4562,11 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
+          <t>Lipofirate</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
           <t>SKU-22321A6F5966</t>
         </is>
       </c>
@@ -4485,7 +4590,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4650,6 +4755,11 @@
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="inlineStr">
         <is>
+          <t>Lipofirate</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
           <t>SKU-C49550B191ED</t>
         </is>
       </c>
@@ -4673,7 +4783,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4830,6 +4940,11 @@
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="inlineStr">
         <is>
+          <t>Rigorixa</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
           <t>SKU-F8E1288C5F49</t>
         </is>
       </c>
@@ -4853,7 +4968,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -5022,6 +5137,11 @@
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="inlineStr">
         <is>
+          <t>Seroflo 25/125 inhaler</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
           <t>SKU-9AFDC80DAB32</t>
         </is>
       </c>
@@ -5045,7 +5165,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5222,6 +5342,11 @@
       </c>
       <c r="AT25" t="inlineStr">
         <is>
+          <t>Seroflo 25/250 inhaler</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
           <t>SKU-8F9F5916851B</t>
         </is>
       </c>
@@ -5245,7 +5370,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5406,6 +5531,11 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
+          <t>Hi-Alfa SR</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
           <t>SKU-E9B7B4B41B79</t>
         </is>
       </c>
@@ -5429,7 +5559,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5600,6 +5730,11 @@
       </c>
       <c r="AT27" t="inlineStr">
         <is>
+          <t>Tumeeze Oral Emulsion</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
           <t>SKU-8623551613D0</t>
         </is>
       </c>
@@ -5623,7 +5758,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5792,6 +5927,11 @@
       </c>
       <c r="AT28" t="inlineStr">
         <is>
+          <t>Olopat</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
           <t>SKU-13728269E05D</t>
         </is>
       </c>
@@ -5815,7 +5955,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5984,6 +6124,11 @@
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="inlineStr">
         <is>
+          <t>COSOPT PRESERVATIVE FREE EYE DROP</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
           <t>SKU-D11CC1FEAE77</t>
         </is>
       </c>
@@ -6007,7 +6152,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6178,6 +6323,11 @@
       </c>
       <c r="AT30" t="inlineStr">
         <is>
+          <t>Ubrelvy</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
           <t>SKU-0184C2AD563C</t>
         </is>
       </c>
@@ -6201,7 +6351,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6366,6 +6516,11 @@
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="inlineStr">
         <is>
+          <t>SPERO</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
           <t>SKU-4AB06A248152</t>
         </is>
       </c>
@@ -6389,7 +6544,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6548,6 +6703,11 @@
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="inlineStr">
         <is>
+          <t>Sulmetic</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
           <t>SKU-B26024F96CC9</t>
         </is>
       </c>
@@ -6571,7 +6731,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6738,6 +6898,11 @@
       </c>
       <c r="AT33" t="inlineStr">
         <is>
+          <t>Septolete total lemon and honey</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
           <t>SKU-68BDC597715B</t>
         </is>
       </c>
@@ -6761,7 +6926,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6928,6 +7093,11 @@
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="inlineStr">
         <is>
+          <t>VOCONZA 40MG/ML ORAL SUSPENSION</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
           <t>SKU-BCB87C599880</t>
         </is>
       </c>
@@ -6951,7 +7121,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -7118,6 +7288,11 @@
       </c>
       <c r="AT35" t="inlineStr">
         <is>
+          <t>VALGAN 50MG/ML POWDER FOR ORAL SOLUTION</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
           <t>SKU-04029BF25A54</t>
         </is>
       </c>
@@ -7141,7 +7316,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -7298,6 +7473,11 @@
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="inlineStr">
         <is>
+          <t>Binoven XL</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
           <t>SKU-693DDA5C05E4</t>
         </is>
       </c>
@@ -7321,7 +7501,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -7488,6 +7668,11 @@
       </c>
       <c r="AT37" t="inlineStr">
         <is>
+          <t>Grasustek 6 mg per 0.6 ml</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
           <t>SKU-9356B132F179</t>
         </is>
       </c>
@@ -7511,7 +7696,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -7678,6 +7863,11 @@
       </c>
       <c r="AT38" t="inlineStr">
         <is>
+          <t>Oleovit D3 Oral drops</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
           <t>SKU-99B2C17421B7</t>
         </is>
       </c>
@@ -7701,7 +7891,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7862,6 +8052,11 @@
       </c>
       <c r="AT39" t="inlineStr">
         <is>
+          <t>Setral</t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
           <t>SKU-C169593DFFA0</t>
         </is>
       </c>
@@ -7885,7 +8080,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -8054,6 +8249,11 @@
       </c>
       <c r="AT40" t="inlineStr">
         <is>
+          <t>Remsima SC</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
           <t>SKU-49A2BAE41A9D</t>
         </is>
       </c>
@@ -8077,7 +8277,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -8246,6 +8446,11 @@
       </c>
       <c r="AT41" t="inlineStr">
         <is>
+          <t>Remsima SC with Needle Guard</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
           <t>SKU-8545BB58C4DA</t>
         </is>
       </c>
@@ -8269,7 +8474,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8446,6 +8651,11 @@
       </c>
       <c r="AT42" t="inlineStr">
         <is>
+          <t>Remsima SC Auto injector Pre-filled pen</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
           <t>SKU-EDDF558A90B8</t>
         </is>
       </c>
@@ -8469,7 +8679,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8642,6 +8852,11 @@
       </c>
       <c r="AT43" t="inlineStr">
         <is>
+          <t xml:space="preserve">MAACY </t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
           <t>SKU-6874145E8CEB</t>
         </is>
       </c>
@@ -8665,7 +8880,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8828,6 +9043,11 @@
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="inlineStr">
         <is>
+          <t>Hizentra 1 g per 5 ml vial</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
           <t>SKU-69551090AE5D</t>
         </is>
       </c>
@@ -8851,7 +9071,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -9012,6 +9232,11 @@
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="inlineStr">
         <is>
+          <t>Hizentra 2 g per 10 ml Vial</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
           <t>SKU-DA4BE8B97203</t>
         </is>
       </c>
@@ -9035,7 +9260,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -9200,6 +9425,11 @@
       </c>
       <c r="AT46" t="inlineStr">
         <is>
+          <t>Hizentra 4 g per 20 ml Vial</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
           <t>SKU-B0F45F59436F</t>
         </is>
       </c>
@@ -9223,7 +9453,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -9388,6 +9618,11 @@
       </c>
       <c r="AT47" t="inlineStr">
         <is>
+          <t>Hizentra 10 g per 50 ml vial</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
           <t>SKU-7811029BBBE2</t>
         </is>
       </c>
@@ -9411,7 +9646,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9568,6 +9803,11 @@
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="inlineStr">
         <is>
+          <t>Avialis</t>
+        </is>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
           <t>SKU-7B4969E74A32</t>
         </is>
       </c>
@@ -9591,7 +9831,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9760,6 +10000,11 @@
       </c>
       <c r="AT49" t="inlineStr">
         <is>
+          <t>Cefuzime</t>
+        </is>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
           <t>SKU-D92A82484A07</t>
         </is>
       </c>
@@ -9783,7 +10028,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -9942,6 +10187,11 @@
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="inlineStr">
         <is>
+          <t>Gemorya</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
           <t>SKU-C24167F76FE8</t>
         </is>
       </c>
@@ -9965,7 +10215,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -10124,6 +10374,11 @@
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="inlineStr">
         <is>
+          <t>Gemorya</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
           <t>SKU-821C60E42F2C</t>
         </is>
       </c>
@@ -10147,7 +10402,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -10316,6 +10571,11 @@
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="inlineStr">
         <is>
+          <t>Rinvoq</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
           <t>SKU-8FFAA0C39D95</t>
         </is>
       </c>
@@ -10339,7 +10599,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10498,6 +10758,11 @@
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="inlineStr">
         <is>
+          <t>TENOVAS</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
           <t>SKU-371207E0B3A5</t>
         </is>
       </c>
@@ -10521,7 +10786,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10682,6 +10947,11 @@
       </c>
       <c r="AT54" t="inlineStr">
         <is>
+          <t>Tenovas</t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
           <t>SKU-884709EA0199</t>
         </is>
       </c>
@@ -10705,7 +10975,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -10878,6 +11148,11 @@
       </c>
       <c r="AT55" t="inlineStr">
         <is>
+          <t>Apixaban BOS</t>
+        </is>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
           <t>SKU-965D00C20C6A</t>
         </is>
       </c>
@@ -10901,7 +11176,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -11074,6 +11349,11 @@
       </c>
       <c r="AT56" t="inlineStr">
         <is>
+          <t>Apixaban BOS</t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
           <t>SKU-9CEB32D3BED0</t>
         </is>
       </c>
@@ -11097,7 +11377,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -11268,6 +11548,11 @@
       </c>
       <c r="AT57" t="inlineStr">
         <is>
+          <t>PIANKA 50 MG/ 5 ML SYRUP</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
           <t>SKU-3989F3BE6ED3</t>
         </is>
       </c>
@@ -11291,7 +11576,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -11458,6 +11743,11 @@
       </c>
       <c r="AT58" t="inlineStr">
         <is>
+          <t>Fermata</t>
+        </is>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
           <t>SKU-FDBBE8B38A5F</t>
         </is>
       </c>
@@ -11481,7 +11771,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -11650,6 +11940,11 @@
       </c>
       <c r="AT59" t="inlineStr">
         <is>
+          <t xml:space="preserve">IROREST FCT	</t>
+        </is>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
           <t>SKU-3BB7DD11CC84</t>
         </is>
       </c>
@@ -11673,7 +11968,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -11848,6 +12143,11 @@
       </c>
       <c r="AT60" t="inlineStr">
         <is>
+          <t>Lotrell</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
           <t>SKU-BC00609049F6</t>
         </is>
       </c>
@@ -11871,7 +12171,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -12034,6 +12334,11 @@
       </c>
       <c r="AT61" t="inlineStr">
         <is>
+          <t>Palot</t>
+        </is>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
           <t>SKU-0F69AE75D1E0</t>
         </is>
       </c>
@@ -12057,7 +12362,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -12220,6 +12525,11 @@
       </c>
       <c r="AT62" t="inlineStr">
         <is>
+          <t>Palot</t>
+        </is>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
           <t>SKU-3AA011BFB875</t>
         </is>
       </c>
@@ -12243,7 +12553,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -12400,6 +12710,11 @@
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="inlineStr">
         <is>
+          <t>Palot</t>
+        </is>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
           <t>SKU-F58CD7E0A972</t>
         </is>
       </c>
@@ -12423,7 +12738,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -12580,6 +12895,11 @@
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="inlineStr">
         <is>
+          <t>Palot</t>
+        </is>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
           <t>SKU-B333DE5EBD64</t>
         </is>
       </c>
@@ -12603,7 +12923,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12774,6 +13094,11 @@
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="inlineStr">
         <is>
+          <t>Meliglptin</t>
+        </is>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
           <t>SKU-6BFF317870CD</t>
         </is>
       </c>
@@ -12797,7 +13122,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -12972,6 +13297,11 @@
       </c>
       <c r="AT66" t="inlineStr">
         <is>
+          <t>Meliglptin</t>
+        </is>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
           <t>SKU-B26695F0A12E</t>
         </is>
       </c>
@@ -12995,7 +13325,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -13158,6 +13488,11 @@
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="inlineStr">
         <is>
+          <t>Meligamet 50 m / 1000 mg</t>
+        </is>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
           <t>SKU-A2CD192EDB0D</t>
         </is>
       </c>
@@ -13181,7 +13516,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -13352,6 +13687,11 @@
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="inlineStr">
         <is>
+          <t>Meligamet 50 mg / 850 mg</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
           <t>SKU-69EF203E53A8</t>
         </is>
       </c>
@@ -13375,7 +13715,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -13536,6 +13876,11 @@
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="inlineStr">
         <is>
+          <t>Suva</t>
+        </is>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
           <t>SKU-31BACCD760D2</t>
         </is>
       </c>
@@ -13559,7 +13904,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -13732,6 +14077,11 @@
       </c>
       <c r="AT70" t="inlineStr">
         <is>
+          <t>Suva</t>
+        </is>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
           <t>SKU-078019198C58</t>
         </is>
       </c>
@@ -13755,7 +14105,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -13924,6 +14274,11 @@
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="inlineStr">
         <is>
+          <t>Suva</t>
+        </is>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
           <t>SKU-E85DD53F5A38</t>
         </is>
       </c>
@@ -13947,7 +14302,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -14104,6 +14459,11 @@
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="inlineStr">
         <is>
+          <t>Suva</t>
+        </is>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
           <t>SKU-18E714C9FAF1</t>
         </is>
       </c>
@@ -14127,7 +14487,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -14288,6 +14648,11 @@
       </c>
       <c r="AT73" t="inlineStr">
         <is>
+          <t>Rosgan</t>
+        </is>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
           <t>SKU-FF7EFAFBA0A8</t>
         </is>
       </c>
@@ -14311,7 +14676,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -14472,6 +14837,11 @@
       </c>
       <c r="AT74" t="inlineStr">
         <is>
+          <t>Rosgan</t>
+        </is>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
           <t>SKU-9331C30F283E</t>
         </is>
       </c>
@@ -14495,7 +14865,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -14650,6 +15020,11 @@
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="inlineStr">
         <is>
+          <t>Binoven XL</t>
+        </is>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
           <t>SKU-CF3AAD513D8A</t>
         </is>
       </c>
@@ -14673,7 +15048,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -14832,6 +15207,11 @@
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="inlineStr">
         <is>
+          <t>Delstrigo</t>
+        </is>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
           <t>SKU-36BD60CB2784</t>
         </is>
       </c>
@@ -14855,7 +15235,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -15018,6 +15398,11 @@
       </c>
       <c r="AT77" t="inlineStr">
         <is>
+          <t>Nolpaza</t>
+        </is>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
           <t>SKU-C4B66D6ED54E</t>
         </is>
       </c>
@@ -15041,7 +15426,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -15198,6 +15583,11 @@
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="inlineStr">
         <is>
+          <t>Nolpaza</t>
+        </is>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
           <t>SKU-3452F0D35FDD</t>
         </is>
       </c>
@@ -15221,7 +15611,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -15392,6 +15782,11 @@
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="inlineStr">
         <is>
+          <t>XROMI</t>
+        </is>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
           <t>SKU-84008701FFE3</t>
         </is>
       </c>
@@ -15415,7 +15810,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -15574,6 +15969,11 @@
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="inlineStr">
         <is>
+          <t>Geuvid</t>
+        </is>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
           <t>SKU-7778581EE493</t>
         </is>
       </c>
@@ -15597,7 +15997,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -15756,6 +16156,11 @@
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="inlineStr">
         <is>
+          <t>Geuvid</t>
+        </is>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
           <t>SKU-27CB91D03BFB</t>
         </is>
       </c>
@@ -15779,7 +16184,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -15944,6 +16349,11 @@
       </c>
       <c r="AT82" t="inlineStr">
         <is>
+          <t>Teriflunomide BOS</t>
+        </is>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
           <t>SKU-FDACE99D37AC</t>
         </is>
       </c>
@@ -15967,7 +16377,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -16128,6 +16538,11 @@
       </c>
       <c r="AT83" t="inlineStr">
         <is>
+          <t>Olmetrol</t>
+        </is>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
           <t>SKU-2598C27A453C</t>
         </is>
       </c>
@@ -16151,7 +16566,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -16304,6 +16719,11 @@
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="inlineStr">
         <is>
+          <t>Olmetrol</t>
+        </is>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
           <t>SKU-12BB0107BD57</t>
         </is>
       </c>
@@ -16327,7 +16747,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16486,6 +16906,11 @@
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="inlineStr">
         <is>
+          <t>VEGA</t>
+        </is>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
           <t>SKU-D6C758A26BC5</t>
         </is>
       </c>
@@ -16509,7 +16934,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -16666,6 +17091,11 @@
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="inlineStr">
         <is>
+          <t>VEGA</t>
+        </is>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
           <t>SKU-56A35AB2A02B</t>
         </is>
       </c>
@@ -16689,7 +17119,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16852,6 +17282,11 @@
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="inlineStr">
         <is>
+          <t xml:space="preserve">Demsone 10 mg per 5 ml </t>
+        </is>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
           <t>SKU-9199C6659CD7</t>
         </is>
       </c>
@@ -16875,7 +17310,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -17030,6 +17465,11 @@
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="inlineStr">
         <is>
+          <t>Mundell</t>
+        </is>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
           <t>SKU-5CFB6E4062A4</t>
         </is>
       </c>
@@ -17053,7 +17493,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -17210,6 +17650,11 @@
       <c r="AS89" t="inlineStr"/>
       <c r="AT89" t="inlineStr">
         <is>
+          <t>Mundell</t>
+        </is>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
           <t>SKU-E673ECB44D55</t>
         </is>
       </c>
@@ -17233,7 +17678,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -17404,6 +17849,11 @@
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="inlineStr">
         <is>
+          <t>FASENRA Pen</t>
+        </is>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
           <t>SKU-BC7690921479</t>
         </is>
       </c>
@@ -17427,7 +17877,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -17584,6 +18034,11 @@
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="inlineStr">
         <is>
+          <t>PANTOLOC</t>
+        </is>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
           <t>SKU-AFF1FAD8A40F</t>
         </is>
       </c>
@@ -17607,7 +18062,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -17772,6 +18227,11 @@
       </c>
       <c r="AT92" t="inlineStr">
         <is>
+          <t>Sertidep</t>
+        </is>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
           <t>SKU-9CDEF237B0C0</t>
         </is>
       </c>
@@ -17795,7 +18255,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -17966,6 +18426,11 @@
       </c>
       <c r="AT93" t="inlineStr">
         <is>
+          <t>Dopaxol PR</t>
+        </is>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
           <t>SKU-57EAC6D46977</t>
         </is>
       </c>
@@ -17989,7 +18454,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -18156,6 +18621,11 @@
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="inlineStr">
         <is>
+          <t>Dopaxol PR</t>
+        </is>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
           <t>SKU-186E88732C44</t>
         </is>
       </c>
@@ -18179,7 +18649,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -18346,6 +18816,11 @@
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="inlineStr">
         <is>
+          <t>Dopaxol PR</t>
+        </is>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
           <t>SKU-B819F3E56ECB</t>
         </is>
       </c>
@@ -18369,7 +18844,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -18536,6 +19011,11 @@
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="inlineStr">
         <is>
+          <t>Dopaxol PR</t>
+        </is>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
           <t>SKU-60B488A982F6</t>
         </is>
       </c>
@@ -18559,7 +19039,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -18722,6 +19202,11 @@
       </c>
       <c r="AT97" t="inlineStr">
         <is>
+          <t>Difen</t>
+        </is>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
           <t>SKU-95A5A4CBFB91</t>
         </is>
       </c>
@@ -18745,7 +19230,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -18898,6 +19383,11 @@
       <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="inlineStr">
         <is>
+          <t>Osart</t>
+        </is>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
           <t>SKU-768AC93C5522</t>
         </is>
       </c>
@@ -18921,7 +19411,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -19078,6 +19568,11 @@
       <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="inlineStr">
         <is>
+          <t>Osart</t>
+        </is>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
           <t>SKU-D3D6E5F6470A</t>
         </is>
       </c>
@@ -19101,7 +19596,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -19272,6 +19767,11 @@
       </c>
       <c r="AT100" t="inlineStr">
         <is>
+          <t>Zillion</t>
+        </is>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
           <t>SKU-F1226939F817</t>
         </is>
       </c>
@@ -19295,7 +19795,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -19461,6 +19961,11 @@
       </c>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="inlineStr">
+        <is>
+          <t>Aprizla</t>
+        </is>
+      </c>
+      <c r="AU101" t="inlineStr">
         <is>
           <t>SKU-9B74443FC023</t>
         </is>
@@ -19477,7 +19982,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB12"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19523,100 +20028,105 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Level 1*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Level 2*</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Level 3*</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Risk Class *</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sterility</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Model / Catalogue Number</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Single Use</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Legal Manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>UDI-DI</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>GMDN Code / Term</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>SFDA Authorized Representative License No.</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Power Source</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Warranty</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Storage Conditions / En</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Branch id</t>
         </is>
@@ -19648,7 +20158,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -19663,92 +20173,97 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>SKU-51148</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>481.32</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>497</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>100</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19780,7 +20295,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -19795,92 +20310,97 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>SKU-74328</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>29.97</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>498</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>100</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19912,7 +20432,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -19927,92 +20447,97 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>SKU-39316</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>19.68</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T4" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>499</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>100</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20044,7 +20569,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -20059,92 +20584,97 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>SKU-37312</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>424.48</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>500</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>12</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20176,7 +20706,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -20191,92 +20721,97 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>SKU-42264</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>60.89</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>501</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>100</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20308,7 +20843,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -20323,92 +20858,97 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>SKU-71361</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>189.66</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>502</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>100</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>12</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20440,7 +20980,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -20455,92 +20995,97 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>SKU-27120</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>352.98</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>503</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>100</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20572,7 +21117,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -20587,92 +21132,97 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>SKU-30325</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>451.06</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T9" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>504</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>100</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20704,7 +21254,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -20719,92 +21269,97 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>SKU-61929</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>338.15</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Home Health Test</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T10" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>505</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>100</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20836,7 +21391,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -20851,92 +21406,97 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>SKU-44911</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>41.48</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>506</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>100</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>12</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20968,7 +21528,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -20983,92 +21543,97 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>SKU-34108</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>226.04</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T12" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>507</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>100</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>12</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21085,7 +21650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21191,6 +21756,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Ingredients</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
@@ -21226,7 +21801,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -21291,6 +21866,16 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>SKU-7742F87204CF</t>
         </is>
@@ -21327,7 +21912,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -21392,6 +21977,16 @@
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>SKU-FE5DB81E4711</t>
         </is>
@@ -21428,7 +22023,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -21493,6 +22088,16 @@
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>SKU-6E65B4C97092</t>
         </is>
@@ -21529,7 +22134,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -21594,6 +22199,16 @@
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>SKU-044BC98E62CD</t>
         </is>
@@ -21630,7 +22245,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -21695,6 +22310,16 @@
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>SKU-F071A0945E3D</t>
         </is>
@@ -21731,7 +22356,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -21796,6 +22421,16 @@
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>SKU-032BAD354EA9</t>
         </is>
@@ -21832,7 +22467,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -21897,6 +22532,16 @@
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>SKU-6346F2705020</t>
         </is>
@@ -21933,7 +22578,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -21998,6 +22643,16 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>SKU-F7A3CEBC869C</t>
         </is>
@@ -22034,7 +22689,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -22099,6 +22754,16 @@
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>SKU-FC608AB30AA0</t>
         </is>
@@ -22135,7 +22800,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -22200,6 +22865,16 @@
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>SKU-343CBEC40FB9</t>
         </is>
@@ -22236,7 +22911,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -22301,6 +22976,16 @@
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>SKU-446464BCF923</t>
         </is>
@@ -22337,7 +23022,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -22402,6 +23087,16 @@
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>SKU-A6E51F33FEA8</t>
         </is>
@@ -22438,7 +23133,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -22503,6 +23198,16 @@
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>SKU-EC5D7D0ECB8B</t>
         </is>
@@ -22539,7 +23244,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -22604,6 +23309,16 @@
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>SKU-4B48183BEB38</t>
         </is>
@@ -22640,7 +23355,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -22705,6 +23420,16 @@
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>SKU-3B4B76FEB168</t>
         </is>
@@ -22741,7 +23466,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -22806,6 +23531,16 @@
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>SKU-D2D76BC0AA3B</t>
         </is>
@@ -22842,7 +23577,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -22907,6 +23642,16 @@
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>SKU-B971727D51AD</t>
         </is>
@@ -22943,7 +23688,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -23008,6 +23753,16 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>SKU-A0E86AFA2076</t>
         </is>
@@ -23044,7 +23799,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -23109,6 +23864,16 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>SKU-0263CC03ABF5</t>
         </is>
@@ -23145,7 +23910,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -23210,6 +23975,16 @@
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>SKU-F501DA9B28ED</t>
         </is>

--- a/product_upload/packages/51/file.xlsx
+++ b/product_upload/packages/51/file.xlsx
@@ -1275,8 +1275,16 @@
           <t>0245219169-204-616753251347</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Nevotic</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Nevotic detailed description.</t>
+        </is>
+      </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
@@ -1470,8 +1478,16 @@
           <t>7778552991-949-328735786862</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Zolomid</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Zolomid detailed description.</t>
+        </is>
+      </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
@@ -1653,8 +1669,16 @@
           <t>8891781534-501-713186024783</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Zolomid</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Zolomid detailed description.</t>
+        </is>
+      </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
@@ -1840,8 +1864,16 @@
           <t>1324188168-658-170239069912</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SIMLANDI 40MG/0.4ML SOLUTION FOR INJECTION PFS</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>SIMLANDI 40MG/0.4ML SOLUTION FOR INJECTION PFS detailed description.</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>TABUK PHARMACEUTICAL MANUFACTURING CO.</t>
@@ -2037,8 +2069,16 @@
           <t>5104261788-440-437406018400</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SIMLANDI 40MG/0.4ML SOLUTION FOR INJECTION PFS</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>SIMLANDI 40MG/0.4ML SOLUTION FOR INJECTION PFS detailed description.</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>TABUK PHARMACEUTICAL MANUFACTURING CO.</t>
@@ -2230,8 +2270,16 @@
           <t>7410038334-503-879157509127</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SIMLANDI 80MG/0.4ML SOLUTION FOR INJECTION PFS</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>SIMLANDI 80MG/0.4ML SOLUTION FOR INJECTION PFS detailed description.</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>TABUK PHARMACEUTICAL MANUFACTURING CO.</t>
@@ -3824,8 +3872,16 @@
           <t>0994893261-100-650888230168</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ EpiPen 150 mcg per  0.3 ml</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>EpiPen 150 mcg per  0.3 ml detailed description.</t>
+        </is>
+      </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
@@ -4015,8 +4071,16 @@
           <t>7767492914-458-898613060894</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RYALTRIS</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>RYALTRIS detailed description.</t>
+        </is>
+      </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
@@ -4206,8 +4270,16 @@
           <t>8787984756-991-172001922736</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RYALTRIS</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>RYALTRIS detailed description.</t>
+        </is>
+      </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
@@ -4401,8 +4473,16 @@
           <t>4766143472-164-859815881705</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Lipofirate</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Lipofirate detailed description.</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
           <t>AL RAZI PHARMA INDUSTRIES FACTORY LTD</t>
@@ -4598,8 +4678,16 @@
           <t>9740164033-966-908106991835</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Lipofirate</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Lipofirate detailed description.</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr">
         <is>
           <t>AL RAZI PHARMA INDUSTRIES FACTORY LTD</t>
@@ -4791,8 +4879,16 @@
           <t>4959491976-581-014863634935</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Rigorixa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Rigorixa detailed description.</t>
+        </is>
+      </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
@@ -5378,8 +5474,16 @@
           <t>8689566475-836-715846151066</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Hi-Alfa SR</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Hi-Alfa SR detailed description.</t>
+        </is>
+      </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
@@ -6552,8 +6656,16 @@
           <t>8043461778-754-589831745985</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Sulmetic</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Sulmetic detailed description.</t>
+        </is>
+      </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
@@ -6739,8 +6851,16 @@
           <t>1326339144-538-924492865164</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Septolete total lemon and honey</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Septolete total lemon and honey detailed description.</t>
+        </is>
+      </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
@@ -7129,8 +7249,16 @@
           <t>1151558168-350-124048589230</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VALGAN 50MG/ML POWDER FOR ORAL SOLUTION</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>VALGAN 50MG/ML POWDER FOR ORAL SOLUTION detailed description.</t>
+        </is>
+      </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
@@ -7324,8 +7452,16 @@
           <t>2233061716-208-022441223199</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Binoven XL</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Binoven XL detailed description.</t>
+        </is>
+      </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
@@ -7509,8 +7645,16 @@
           <t>6980018963-623-367195653985</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Grasustek 6 mg per 0.6 ml</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Grasustek 6 mg per 0.6 ml detailed description.</t>
+        </is>
+      </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
@@ -7704,8 +7848,16 @@
           <t>7269552180-921-739561296584</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Oleovit D3 Oral drops</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Oleovit D3 Oral drops detailed description.</t>
+        </is>
+      </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
@@ -7899,8 +8051,16 @@
           <t>2801342053-590-886207838743</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Setral</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Setral detailed description.</t>
+        </is>
+      </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
@@ -8088,8 +8248,16 @@
           <t>7114369362-929-037142544920</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Remsima SC</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Remsima SC detailed description.</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr">
         <is>
           <t>Jazeera Pharmaceutical Industries (JPI)</t>
@@ -8285,8 +8453,16 @@
           <t>3267869783-974-921769754744</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Remsima SC with Needle Guard</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Remsima SC with Needle Guard detailed description.</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr">
         <is>
           <t>Jazeera Pharmaceutical Industries (JPI)</t>
@@ -8888,8 +9064,16 @@
           <t>0806443188-750-832732881012</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Hizentra 1 g per 5 ml vial</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Hizentra 1 g per 5 ml vial detailed description.</t>
+        </is>
+      </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
@@ -9079,8 +9263,16 @@
           <t>4079229144-047-785099790242</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Hizentra 2 g per 10 ml Vial</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Hizentra 2 g per 10 ml Vial detailed description.</t>
+        </is>
+      </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
@@ -9268,8 +9460,16 @@
           <t>8180421321-174-697049479196</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Hizentra 4 g per 20 ml Vial</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Hizentra 4 g per 20 ml Vial detailed description.</t>
+        </is>
+      </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
@@ -9461,8 +9661,16 @@
           <t>6858829452-153-997751827401</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Hizentra 10 g per 50 ml vial</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Hizentra 10 g per 50 ml vial detailed description.</t>
+        </is>
+      </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
@@ -9654,8 +9862,16 @@
           <t>7364605012-010-016204571396</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Avialis</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Avialis detailed description.</t>
+        </is>
+      </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
@@ -10036,8 +10252,16 @@
           <t>5243879413-913-195652470328</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Gemorya</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Gemorya detailed description.</t>
+        </is>
+      </c>
       <c r="I50" t="inlineStr">
         <is>
           <t>Jazeera Pharmaceutical Industries (JPI)</t>
@@ -10223,8 +10447,16 @@
           <t>9872196255-724-356868835277</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Gemorya</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Gemorya detailed description.</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr">
         <is>
           <t>Jazeera Pharmaceutical Industries (JPI)</t>
@@ -10607,8 +10839,16 @@
           <t>7911360978-690-097566275123</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TENOVAS</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>TENOVAS detailed description.</t>
+        </is>
+      </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
@@ -10794,8 +11034,16 @@
           <t>4385272243-249-918794314202</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Tenovas</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Tenovas detailed description.</t>
+        </is>
+      </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
@@ -11584,8 +11832,16 @@
           <t>1595067093-158-293057465107</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Fermata</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Fermata detailed description.</t>
+        </is>
+      </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
@@ -12179,8 +12435,16 @@
           <t>2813713974-724-914475297177</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Palot</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Palot detailed description.</t>
+        </is>
+      </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
@@ -12370,8 +12634,16 @@
           <t>4835707767-807-095487191614</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Palot</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Palot detailed description.</t>
+        </is>
+      </c>
       <c r="I62" t="n">
         <v>0</v>
       </c>
@@ -12561,8 +12833,16 @@
           <t>0035714442-271-790069042284</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Palot</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Palot detailed description.</t>
+        </is>
+      </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
@@ -12746,8 +13026,16 @@
           <t>4115306339-421-872841779226</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Palot</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Palot detailed description.</t>
+        </is>
+      </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
@@ -13723,8 +14011,16 @@
           <t>9629871316-649-576861817706</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Suva</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Suva detailed description.</t>
+        </is>
+      </c>
       <c r="I69" t="inlineStr">
         <is>
           <t>SAUDI PHARMACEUTICAL INDUSTRIES</t>
@@ -14310,8 +14606,16 @@
           <t>0285609906-433-650913962688</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Suva</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Suva detailed description.</t>
+        </is>
+      </c>
       <c r="I72" t="inlineStr">
         <is>
           <t>SAUDI PHARMACEUTICAL INDUSTRIES</t>
@@ -14495,8 +14799,16 @@
           <t>1738114863-065-482677136543</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Rosgan</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Rosgan detailed description.</t>
+        </is>
+      </c>
       <c r="I73" t="n">
         <v>0</v>
       </c>
@@ -14684,8 +14996,16 @@
           <t>6788307638-743-671211932266</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Rosgan</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Rosgan detailed description.</t>
+        </is>
+      </c>
       <c r="I74" t="n">
         <v>0</v>
       </c>
@@ -14873,8 +15193,16 @@
           <t>9031268355-852-514271730251</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Binoven XL</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Binoven XL detailed description.</t>
+        </is>
+      </c>
       <c r="I75" t="n">
         <v>0</v>
       </c>
@@ -15056,8 +15384,16 @@
           <t>2005451508-956-834052717676</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Delstrigo</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Delstrigo detailed description.</t>
+        </is>
+      </c>
       <c r="I76" t="n">
         <v>0</v>
       </c>
@@ -15243,8 +15579,16 @@
           <t>8676039899-394-980454723764</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Nolpaza</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Nolpaza detailed description.</t>
+        </is>
+      </c>
       <c r="I77" t="n">
         <v>0</v>
       </c>
@@ -15434,8 +15778,16 @@
           <t>3732602782-808-501776809879</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Nolpaza</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Nolpaza detailed description.</t>
+        </is>
+      </c>
       <c r="I78" t="n">
         <v>0</v>
       </c>
@@ -15818,8 +16170,16 @@
           <t>0484698231-967-718739233631</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Geuvid</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Geuvid detailed description.</t>
+        </is>
+      </c>
       <c r="I80" t="n">
         <v>0</v>
       </c>
@@ -16005,8 +16365,16 @@
           <t>8480381430-625-247231026052</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Geuvid</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Geuvid detailed description.</t>
+        </is>
+      </c>
       <c r="I81" t="n">
         <v>0</v>
       </c>
@@ -16192,8 +16560,16 @@
           <t>5246286434-868-226562733622</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Teriflunomide BOS</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Teriflunomide BOS detailed description.</t>
+        </is>
+      </c>
       <c r="I82" t="inlineStr">
         <is>
           <t>Boston Oncology Arabia</t>
@@ -16385,8 +16761,16 @@
           <t>2826054084-223-625559140256</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Olmetrol</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Olmetrol detailed description.</t>
+        </is>
+      </c>
       <c r="I83" t="n">
         <v>0</v>
       </c>
@@ -16574,8 +16958,16 @@
           <t>9970690659-991-388116165643</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Olmetrol</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Olmetrol detailed description.</t>
+        </is>
+      </c>
       <c r="I84" t="n">
         <v>0</v>
       </c>
@@ -16755,8 +17147,16 @@
           <t>7025357271-332-962970158129</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VEGA</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>VEGA detailed description.</t>
+        </is>
+      </c>
       <c r="I85" t="n">
         <v>0</v>
       </c>
@@ -16942,8 +17342,16 @@
           <t>2003488043-828-356417136035</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VEGA</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>VEGA detailed description.</t>
+        </is>
+      </c>
       <c r="I86" t="n">
         <v>0</v>
       </c>
@@ -17127,8 +17535,16 @@
           <t>9029804316-979-407463715462</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Demsone 10 mg per 5 ml</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Demsone 10 mg per 5 ml detailed description.</t>
+        </is>
+      </c>
       <c r="I87" t="n">
         <v>0</v>
       </c>
@@ -17318,8 +17734,16 @@
           <t>1304386149-854-928871436230</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Mundell</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Mundell detailed description.</t>
+        </is>
+      </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
@@ -17501,8 +17925,16 @@
           <t>2484657795-734-731317400157</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Mundell</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Mundell detailed description.</t>
+        </is>
+      </c>
       <c r="I89" t="n">
         <v>0</v>
       </c>
@@ -17885,8 +18317,16 @@
           <t>6336770159-399-960329094192</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PANTOLOC</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>PANTOLOC detailed description.</t>
+        </is>
+      </c>
       <c r="I91" t="n">
         <v>0</v>
       </c>
@@ -18070,8 +18510,16 @@
           <t>3396962136-432-684188578702</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Sertidep</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Sertidep detailed description.</t>
+        </is>
+      </c>
       <c r="I92" t="inlineStr">
         <is>
           <t>APEX PHARMA Saudi</t>
@@ -19047,8 +19495,16 @@
           <t>5597171305-442-504288502464</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Difen</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Difen detailed description.</t>
+        </is>
+      </c>
       <c r="I97" t="n">
         <v>0</v>
       </c>
@@ -19238,8 +19694,16 @@
           <t>2416517822-658-336682382371</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Osart</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Osart detailed description.</t>
+        </is>
+      </c>
       <c r="I98" t="n">
         <v>0</v>
       </c>
@@ -19419,8 +19883,16 @@
           <t>6552058138-794-010370713788</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Osart</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Osart detailed description.</t>
+        </is>
+      </c>
       <c r="I99" t="n">
         <v>0</v>
       </c>

--- a/product_upload/packages/51/file.xlsx
+++ b/product_upload/packages/51/file.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -20500,7 +20500,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -22122,7 +22122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22203,40 +22203,45 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>Size unit</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Manufacturer *</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Period After Opening.1</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Warnings</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Manufacturer Name</t>
-        </is>
-      </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -22316,38 +22321,43 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>232.85</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>SKU-7742F87204CF</t>
         </is>
@@ -22427,38 +22437,43 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>360.81</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>SKU-FE5DB81E4711</t>
         </is>
@@ -22538,38 +22553,43 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>255.96</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>SKU-6E65B4C97092</t>
         </is>
@@ -22649,38 +22669,43 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>229.56</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>SKU-044BC98E62CD</t>
         </is>
@@ -22760,38 +22785,43 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>262.69</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>SKU-F071A0945E3D</t>
         </is>
@@ -22871,38 +22901,43 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>468.68</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>SKU-032BAD354EA9</t>
         </is>
@@ -22982,38 +23017,43 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>67.8</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>SKU-6346F2705020</t>
         </is>
@@ -23093,38 +23133,43 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>16.04</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>SKU-F7A3CEBC869C</t>
         </is>
@@ -23204,38 +23249,43 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>62.53</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>SKU-FC608AB30AA0</t>
         </is>
@@ -23315,38 +23365,43 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>366.89</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>SKU-343CBEC40FB9</t>
         </is>
@@ -23426,38 +23481,43 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>228.32</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>SKU-446464BCF923</t>
         </is>
@@ -23537,38 +23597,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>174.89</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>SKU-A6E51F33FEA8</t>
         </is>
@@ -23648,38 +23713,43 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>467.23</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>SKU-EC5D7D0ECB8B</t>
         </is>
@@ -23759,38 +23829,43 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>53.35</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>SKU-4B48183BEB38</t>
         </is>
@@ -23870,38 +23945,43 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>356.53</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>SKU-3B4B76FEB168</t>
         </is>
@@ -23981,38 +24061,43 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>297.69</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>SKU-D2D76BC0AA3B</t>
         </is>
@@ -24092,38 +24177,43 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>142.6</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>SKU-B971727D51AD</t>
         </is>
@@ -24203,38 +24293,43 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>285.01</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>SKU-A0E86AFA2076</t>
         </is>
@@ -24314,38 +24409,43 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>362.92</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>SKU-0263CC03ABF5</t>
         </is>
@@ -24425,38 +24525,43 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>64.18000000000001</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>SKU-F501DA9B28ED</t>
         </is>
